--- a/jogos_2025-10-26.xlsx
+++ b/jogos_2025-10-26.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Hang Yuan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hang Yuan</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>13.32</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4326,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45956.34375</v>
+        <v>45956.33333333334</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,55 +6345,55 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA46" t="n">
         <v>2.3</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45956.35416666666</v>
+        <v>45956.34375</v>
       </c>
     </row>
     <row r="47">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45956.35763888889</v>
+        <v>45956.35416666666</v>
       </c>
     </row>
     <row r="56">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7680,10 +7680,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7723,27 +7723,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7809,10 +7809,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45956.36458333334</v>
+        <v>45956.35763888889</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="M58" t="n">
-        <v>3.95</v>
+        <v>3.58</v>
       </c>
       <c r="N58" t="n">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,16 +7932,16 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45956.375</v>
+        <v>45956.36458333334</v>
       </c>
     </row>
     <row r="59">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,16 +10254,16 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -10308,22 +10308,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45956.38541666666</v>
+        <v>45956.375</v>
       </c>
     </row>
     <row r="79">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45956.39583333334</v>
+        <v>45956.38541666666</v>
       </c>
     </row>
     <row r="80">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11464,12 +11464,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45956.41666666666</v>
+        <v>45956.39583333334</v>
       </c>
     </row>
     <row r="87">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.35</v>
+        <v>6.4</v>
       </c>
       <c r="M87" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="N87" t="n">
-        <v>8.5</v>
+        <v>1.43</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,16 +11673,16 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="M90" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N90" t="n">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,16 +12060,16 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12453,10 +12453,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45956.4375</v>
+        <v>45956.41666666666</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12711,10 +12711,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45956.4375</v>
+        <v>45956.41666666666</v>
       </c>
     </row>
     <row r="96">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13614,10 +13614,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45956.44791666666</v>
+        <v>45956.4375</v>
       </c>
     </row>
     <row r="105">
@@ -13915,27 +13915,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45956.45833333334</v>
+        <v>45956.4375</v>
       </c>
     </row>
     <row r="106">
@@ -14044,12 +14044,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="M106" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N106" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45956.45833333334</v>
+        <v>45956.44791666666</v>
       </c>
     </row>
     <row r="107">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,16 +14382,16 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="M111" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="N111" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,16 +14898,16 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.38</v>
+        <v>4.5</v>
       </c>
       <c r="M115" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="N115" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="Z115" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16242,22 +16242,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16366,27 +16366,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45956.47916666666</v>
+        <v>45956.45833333334</v>
       </c>
     </row>
     <row r="125">
@@ -16495,12 +16495,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16581,10 +16581,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45956.47916666666</v>
+        <v>45956.45833333334</v>
       </c>
     </row>
     <row r="126">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,10 +16923,10 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="M128" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N128" t="n">
         <v>3</v>
@@ -16962,16 +16962,16 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45956.48958333334</v>
+        <v>45956.47916666666</v>
       </c>
     </row>
     <row r="130">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45956.5</v>
+        <v>45956.47916666666</v>
       </c>
     </row>
     <row r="131">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45956.5</v>
+        <v>45956.48958333334</v>
       </c>
     </row>
     <row r="132">
@@ -17403,22 +17403,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19116,13 +19116,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="Y145" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA145" t="n">
         <v>0</v>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19245,13 +19245,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19284,10 +19284,10 @@
         <v>0</v>
       </c>
       <c r="Y146" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA146" t="n">
         <v>0</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19632,13 +19632,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -19671,10 +19671,10 @@
         <v>0</v>
       </c>
       <c r="Y149" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z149" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA149" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19761,13 +19761,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -19800,10 +19800,10 @@
         <v>0</v>
       </c>
       <c r="Y150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z150" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA150" t="n">
         <v>0</v>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20664,13 +20664,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -20703,10 +20703,10 @@
         <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z157" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA157" t="n">
         <v>0</v>
@@ -20757,22 +20757,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -20922,13 +20922,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -20961,10 +20961,10 @@
         <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z159" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA159" t="n">
         <v>0</v>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21219,10 +21219,10 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z161" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA161" t="n">
         <v>0</v>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21567,13 +21567,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -21606,10 +21606,10 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z164" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA164" t="n">
         <v>0</v>
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21696,13 +21696,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="M165" t="n">
-        <v>3.86</v>
+        <v>3.38</v>
       </c>
       <c r="N165" t="n">
-        <v>3.2</v>
+        <v>3.56</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -21735,10 +21735,10 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="Z165" t="n">
-        <v>2.75</v>
+        <v>1.61</v>
       </c>
       <c r="AA165" t="n">
         <v>0</v>
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22212,13 +22212,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22251,10 +22251,10 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z169" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA169" t="n">
         <v>0</v>
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22341,13 +22341,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22470,13 +22470,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.27</v>
+        <v>2.73</v>
       </c>
       <c r="M171" t="n">
-        <v>5.6</v>
+        <v>3.06</v>
       </c>
       <c r="N171" t="n">
-        <v>8.6</v>
+        <v>2.59</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -22509,16 +22509,16 @@
         <v>0</v>
       </c>
       <c r="Y171" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z171" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AB171" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22857,13 +22857,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>2.73</v>
+        <v>2.11</v>
       </c>
       <c r="M175" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="N175" t="n">
-        <v>2.59</v>
+        <v>3.35</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23244,13 +23244,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23373,13 +23373,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23412,10 +23412,10 @@
         <v>0</v>
       </c>
       <c r="Y178" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z178" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA178" t="n">
         <v>0</v>
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23502,13 +23502,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -23541,10 +23541,10 @@
         <v>0</v>
       </c>
       <c r="Y179" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z179" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA179" t="n">
         <v>0</v>
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23631,13 +23631,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -23670,10 +23670,10 @@
         <v>0</v>
       </c>
       <c r="Y180" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z180" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA180" t="n">
         <v>0</v>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -23799,10 +23799,10 @@
         <v>0</v>
       </c>
       <c r="Y181" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA181" t="n">
         <v>0</v>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23889,13 +23889,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -23928,10 +23928,10 @@
         <v>0</v>
       </c>
       <c r="Y182" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z182" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA182" t="n">
         <v>0</v>
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24018,13 +24018,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24663,13 +24663,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -24702,10 +24702,10 @@
         <v>0</v>
       </c>
       <c r="Y188" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA188" t="n">
         <v>0</v>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24792,13 +24792,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -24921,13 +24921,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -24960,10 +24960,10 @@
         <v>0</v>
       </c>
       <c r="Y190" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z190" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA190" t="n">
         <v>0</v>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25050,13 +25050,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>2.11</v>
+        <v>2.52</v>
       </c>
       <c r="M191" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="N191" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25089,10 +25089,10 @@
         <v>0</v>
       </c>
       <c r="Y191" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z191" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA191" t="n">
         <v>0</v>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25218,10 +25218,10 @@
         <v>0</v>
       </c>
       <c r="Y192" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z192" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA192" t="n">
         <v>0</v>
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25308,13 +25308,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25347,10 +25347,10 @@
         <v>0</v>
       </c>
       <c r="Y193" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z193" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA193" t="n">
         <v>0</v>
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25437,13 +25437,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -25476,10 +25476,10 @@
         <v>0</v>
       </c>
       <c r="Y194" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA194" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25566,13 +25566,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -25605,10 +25605,10 @@
         <v>0</v>
       </c>
       <c r="Y195" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z195" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA195" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26211,13 +26211,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26250,16 +26250,16 @@
         <v>0</v>
       </c>
       <c r="Y200" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z200" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA200" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB200" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC200" t="n">
         <v>0</v>
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26727,13 +26727,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -26766,10 +26766,10 @@
         <v>0</v>
       </c>
       <c r="Y204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z204" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA204" t="n">
         <v>0</v>
@@ -26820,22 +26820,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26856,13 +26856,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1.33</v>
+        <v>3.35</v>
       </c>
       <c r="M205" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N205" t="n">
-        <v>9.5</v>
+        <v>2.05</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -26895,10 +26895,10 @@
         <v>0</v>
       </c>
       <c r="Y205" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="Z205" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA205" t="n">
         <v>0</v>
@@ -26949,22 +26949,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -26985,13 +26985,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27024,10 +27024,10 @@
         <v>0</v>
       </c>
       <c r="Y206" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA206" t="n">
         <v>0</v>
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27114,13 +27114,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27153,10 +27153,10 @@
         <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z207" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA207" t="n">
         <v>0</v>
@@ -27207,22 +27207,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27243,13 +27243,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="M208" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N208" t="n">
-        <v>4.15</v>
+        <v>2.75</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27282,10 +27282,10 @@
         <v>0</v>
       </c>
       <c r="Y208" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Z208" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA208" t="n">
         <v>0</v>
@@ -27336,22 +27336,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27372,13 +27372,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27630,13 +27630,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="M211" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N211" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -27669,10 +27669,10 @@
         <v>0</v>
       </c>
       <c r="Y211" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z211" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA211" t="n">
         <v>0</v>
@@ -27723,22 +27723,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27759,13 +27759,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="M212" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N212" t="n">
-        <v>2.7</v>
+        <v>9.5</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -27798,10 +27798,10 @@
         <v>0</v>
       </c>
       <c r="Y212" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Z212" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AA212" t="n">
         <v>0</v>
@@ -27852,22 +27852,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -29952,49 +29952,49 @@
         </is>
       </c>
       <c r="L229" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M229" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N229" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>0</v>
+      </c>
+      <c r="R229" t="n">
+        <v>0</v>
+      </c>
+      <c r="S229" t="n">
+        <v>0</v>
+      </c>
+      <c r="T229" t="n">
+        <v>0</v>
+      </c>
+      <c r="U229" t="n">
+        <v>0</v>
+      </c>
+      <c r="V229" t="n">
+        <v>0</v>
+      </c>
+      <c r="W229" t="n">
+        <v>0</v>
+      </c>
+      <c r="X229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z229" t="n">
         <v>2</v>
-      </c>
-      <c r="M229" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N229" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="O229" t="n">
-        <v>0</v>
-      </c>
-      <c r="P229" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
-      <c r="R229" t="n">
-        <v>0</v>
-      </c>
-      <c r="S229" t="n">
-        <v>0</v>
-      </c>
-      <c r="T229" t="n">
-        <v>0</v>
-      </c>
-      <c r="U229" t="n">
-        <v>0</v>
-      </c>
-      <c r="V229" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W229" t="n">
-        <v>0</v>
-      </c>
-      <c r="X229" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y229" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z229" t="n">
-        <v>1.8</v>
       </c>
       <c r="AA229" t="n">
         <v>0</v>
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="M230" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N230" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="Z230" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30210,13 +30210,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>2.07</v>
+        <v>3.25</v>
       </c>
       <c r="M231" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N231" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30249,10 +30249,10 @@
         <v>0</v>
       </c>
       <c r="Y231" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="Z231" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AA231" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30339,13 +30339,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="M232" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N232" t="n">
-        <v>2.25</v>
+        <v>4.05</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -30369,7 +30369,7 @@
         <v>0</v>
       </c>
       <c r="V232" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W232" t="n">
         <v>0</v>
@@ -30378,10 +30378,10 @@
         <v>0</v>
       </c>
       <c r="Y232" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Z232" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AA232" t="n">
         <v>0</v>
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31113,13 +31113,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31152,10 +31152,10 @@
         <v>0</v>
       </c>
       <c r="Y238" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z238" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA238" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31500,13 +31500,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -31539,10 +31539,10 @@
         <v>0</v>
       </c>
       <c r="Y241" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z241" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA241" t="n">
         <v>0</v>
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31887,13 +31887,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -31926,10 +31926,10 @@
         <v>0</v>
       </c>
       <c r="Y244" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z244" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA244" t="n">
         <v>0</v>
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32532,13 +32532,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>1.38</v>
+        <v>2.8</v>
       </c>
       <c r="M249" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="N249" t="n">
-        <v>7.8</v>
+        <v>2.6</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -32571,10 +32571,10 @@
         <v>0</v>
       </c>
       <c r="Y249" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="Z249" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AA249" t="n">
         <v>0</v>
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32661,13 +32661,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -32700,10 +32700,10 @@
         <v>0</v>
       </c>
       <c r="Y250" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z250" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA250" t="n">
         <v>0</v>
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33435,13 +33435,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="M256" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N256" t="n">
-        <v>10.5</v>
+        <v>7.1</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -33477,7 +33477,7 @@
         <v>1.7</v>
       </c>
       <c r="Z256" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AA256" t="n">
         <v>0</v>
@@ -33528,22 +33528,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33564,13 +33564,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M257" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -33603,10 +33603,10 @@
         <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z257" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA257" t="n">
         <v>0</v>
@@ -33657,22 +33657,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33693,13 +33693,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N258" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -33732,10 +33732,10 @@
         <v>0</v>
       </c>
       <c r="Y258" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z258" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA258" t="n">
         <v>0</v>
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,22 +34044,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34173,22 +34173,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34689,22 +34689,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34725,13 +34725,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N266" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -34764,10 +34764,10 @@
         <v>0</v>
       </c>
       <c r="Y266" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z266" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA266" t="n">
         <v>0</v>
@@ -34818,22 +34818,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34947,22 +34947,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -34983,13 +34983,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="M268" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N268" t="n">
-        <v>4.5</v>
+        <v>3.51</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -35022,10 +35022,10 @@
         <v>0</v>
       </c>
       <c r="Y268" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Z268" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AA268" t="n">
         <v>0</v>
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35241,13 +35241,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="M270" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N270" t="n">
-        <v>3.51</v>
+        <v>5.1</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -35280,10 +35280,10 @@
         <v>0</v>
       </c>
       <c r="Y270" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z270" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AA270" t="n">
         <v>0</v>
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35370,13 +35370,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M271" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -35409,10 +35409,10 @@
         <v>0</v>
       </c>
       <c r="Y271" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z271" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA271" t="n">
         <v>0</v>
@@ -35463,22 +35463,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35850,7 +35850,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36366,22 +36366,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36495,22 +36495,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36634,12 +36634,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37150,12 +37150,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G285" t="n">
